--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104865</v>
+        <v>104868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104868</v>
+        <v>104869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482464</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136482415</v>
       </c>
       <c r="B3" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482464</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,11 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -798,7 +794,7 @@
         <v>136482415</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,11 +826,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -917,7 +909,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104895</v>
+        <v>104968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8750-2025 artfynd.xlsx
+++ b/artfynd/A 8750-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482464</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136482415</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136482435</v>
       </c>
       <c r="B4" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
